--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_9_R1.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_9_R1.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.454</v>
+        <v>1.6511</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6063</v>
+        <v>4.837</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.1523</v>
+        <v>-3.1859</v>
       </c>
       <c r="G2" t="n">
         <v>0.9035</v>
@@ -610,13 +610,13 @@
         <v>0.6959</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6433</v>
+        <v>0.8404</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7957</v>
+        <v>1.0264</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1524</v>
+        <v>-0.186</v>
       </c>
       <c r="V2" t="n">
         <v>-0.7886</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4965</v>
+        <v>1.556</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6215</v>
+        <v>4.2859</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.125</v>
+        <v>-2.7299</v>
       </c>
       <c r="G3" t="n">
         <v>0.1925</v>
@@ -688,13 +688,13 @@
         <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9999</v>
+        <v>1.0594</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2003</v>
+        <v>0.4641</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2002</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>0.5361</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4532</v>
+        <v>1.3576</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.6323</v>
+        <v>-1.5262</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0854</v>
+        <v>2.8838</v>
       </c>
       <c r="G4" t="n">
         <v>-0.8734</v>
@@ -766,13 +766,13 @@
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9348</v>
+        <v>0.8393</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0193</v>
+        <v>0.0868</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9542</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DIALLO</t>
+          <t>N. NEDOVIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9836</v>
+        <v>0.8342000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4052</v>
+        <v>0.4655</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4216</v>
+        <v>0.3687</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7704</v>
+        <v>0.6921</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2533</v>
+        <v>0.7791</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0238</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7282</v>
+        <v>0.2451</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0657</v>
+        <v>0.1715</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6625</v>
+        <v>0.0736</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.4986</v>
+        <v>0.447</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8123</v>
+        <v>0.6075</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6862</v>
+        <v>-0.1605</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9278</v>
+        <v>0.9278</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6096</v>
+        <v>0.57</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9243</v>
+        <v>0.2203</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6853</v>
+        <v>0.3497</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0722</v>
+        <v>-1.3558</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. NEDOVIC</t>
+          <t>A. DIALLO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2712</v>
+        <v>0.6851</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0369</v>
+        <v>1.0394</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2343</v>
+        <v>-0.3544</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6921</v>
+        <v>-0.7704</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7791</v>
+        <v>0.2533</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-1.0238</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2451</v>
+        <v>1.7282</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1715</v>
+        <v>1.0657</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0736</v>
+        <v>0.6625</v>
       </c>
       <c r="M6" t="n">
-        <v>0.447</v>
+        <v>-2.4986</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6075</v>
+        <v>-0.8123</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1605</v>
+        <v>-1.6862</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9278</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>0.007</v>
+        <v>1.3111</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2082</v>
+        <v>0.5586</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2153</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.3558</v>
+        <v>1.0722</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1027</v>
+        <v>0.2879</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2483</v>
+        <v>-0.1304</v>
       </c>
       <c r="F7" t="n">
-        <v>0.351</v>
+        <v>0.4183</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0247</v>
@@ -1000,13 +1000,13 @@
         <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1046</v>
+        <v>0.0806</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1942</v>
+        <v>0.2614</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9564</v>
+        <v>-0.3455</v>
       </c>
       <c r="E8" t="n">
-        <v>0.483</v>
+        <v>0.825</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4394</v>
+        <v>-1.1705</v>
       </c>
       <c r="G8" t="n">
         <v>0.0133</v>
@@ -1078,13 +1078,13 @@
         <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0457</v>
+        <v>0.6565</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0114</v>
+        <v>0.3306</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0571</v>
+        <v>0.326</v>
       </c>
       <c r="V8" t="n">
         <v>1.0722</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1284</v>
+        <v>-2.0792</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6468</v>
+        <v>-2.2615</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5183</v>
+        <v>0.1823</v>
       </c>
       <c r="G9" t="n">
         <v>-1.2696</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2829</v>
+        <v>0.3321</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8215</v>
+        <v>-0.4362</v>
       </c>
       <c r="U9" t="n">
-        <v>1.1044</v>
+        <v>0.7683</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6778999999999999</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7051</v>
+        <v>-2.671</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7945</v>
+        <v>-0.13</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.9106</v>
+        <v>-2.541</v>
       </c>
       <c r="G10" t="n">
         <v>-3.0471</v>
@@ -1234,13 +1234,13 @@
         <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.212</v>
+        <v>-0.1779</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4244</v>
+        <v>0.2401</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7877</v>
+        <v>-0.418</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8275</v>
+        <v>-5.0121</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.6393</v>
+        <v>-6.0928</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8118</v>
+        <v>1.0806</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1358</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9805</v>
+        <v>-0.1652</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8883</v>
+        <v>-0.3418</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0922</v>
+        <v>0.1766</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8562</v>
+        <v>-3.7359</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1917</v>
+        <v>1.311899999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.0481</v>
+        <v>-5.048</v>
       </c>
       <c r="G12" t="n">
         <v>-5.319599999999999</v>
@@ -1363,7 +1363,7 @@
         <v>-12.8817</v>
       </c>
       <c r="J12" t="n">
-        <v>8.459299999999997</v>
+        <v>8.459299999999999</v>
       </c>
       <c r="K12" t="n">
         <v>9.480600000000001</v>
@@ -1381,7 +1381,7 @@
         <v>-11.8603</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.4792</v>
+        <v>-3.479200000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>-12.7574</v>
@@ -1390,13 +1390,13 @@
         <v>9.2782</v>
       </c>
       <c r="S12" t="n">
-        <v>4.2261</v>
+        <v>5.346299999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8479000000000002</v>
+        <v>1.9681</v>
       </c>
       <c r="U12" t="n">
-        <v>3.378399999999999</v>
+        <v>3.3783</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2835999999999997</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.8561</v>
+        <v>7.1261</v>
       </c>
       <c r="E13" t="n">
-        <v>8.773</v>
+        <v>6.8857</v>
       </c>
       <c r="F13" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.2404</v>
       </c>
       <c r="G13" t="n">
         <v>4.1128</v>
@@ -1468,13 +1468,13 @@
         <v>1.8556</v>
       </c>
       <c r="S13" t="n">
-        <v>1.903</v>
+        <v>0.1731</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2571</v>
+        <v>0.3699</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3541</v>
+        <v>-0.1968</v>
       </c>
       <c r="V13" t="n">
         <v>2.1444</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>S. FRANCISCO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.508</v>
+        <v>2.2038</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6903</v>
+        <v>0.1556</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8177</v>
+        <v>2.0482</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0899</v>
+        <v>2.522</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9493</v>
+        <v>-0.767</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1406</v>
+        <v>3.289</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5682</v>
+        <v>2.8873</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5314</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0368</v>
+        <v>2.9777</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5217000000000001</v>
+        <v>-0.3654</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4179</v>
+        <v>-0.6766</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1038</v>
+        <v>0.3113</v>
       </c>
       <c r="P14" t="n">
         <v>-0.6959</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3254</v>
+        <v>0.2359</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2819</v>
+        <v>-0.554</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0435</v>
+        <v>0.7899</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7886</v>
+        <v>0.1418</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. FRANCISCO</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0014</v>
+        <v>1.9798</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5521</v>
+        <v>-0.2533</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5535</v>
+        <v>2.233</v>
       </c>
       <c r="G15" t="n">
-        <v>2.522</v>
+        <v>1.0899</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.767</v>
+        <v>0.9493</v>
       </c>
       <c r="I15" t="n">
-        <v>3.289</v>
+        <v>0.1406</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8873</v>
+        <v>0.5682</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.09039999999999999</v>
+        <v>0.5314</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9777</v>
+        <v>0.0368</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3654</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6766</v>
+        <v>0.4179</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3113</v>
+        <v>0.1038</v>
       </c>
       <c r="P15" t="n">
         <v>-0.6959</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9665</v>
+        <v>0.7971</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2617</v>
+        <v>0.3383</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2952</v>
+        <v>0.4589</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1418</v>
+        <v>0.7886</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8625</v>
+        <v>1.5645</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3538</v>
+        <v>0.7077</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5087</v>
+        <v>0.8569</v>
       </c>
       <c r="G16" t="n">
         <v>0.3094</v>
@@ -1702,13 +1702,13 @@
         <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8386</v>
+        <v>-0.1366</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7389</v>
+        <v>-0.3851</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0997</v>
+        <v>0.2484</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. BRAZDEIKIS</t>
+          <t>M. LO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0264</v>
+        <v>0.0367</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3583</v>
+        <v>0.4305</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3319</v>
+        <v>-0.3938</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8183</v>
+        <v>-0.5926</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8618</v>
+        <v>-3.2291</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0435</v>
+        <v>2.6365</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0148</v>
+        <v>1.1347</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4502</v>
+        <v>-1.4516</v>
       </c>
       <c r="L17" t="n">
-        <v>0.465</v>
+        <v>2.5863</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8331</v>
+        <v>-1.7273</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4116</v>
+        <v>-1.7775</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4216</v>
+        <v>0.0502</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0457</v>
+        <v>-0.8167</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5149</v>
+        <v>-0.7585</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4692</v>
+        <v>-0.0582</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1418</v>
+        <v>1.214</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1418</v>
+        <v>1.214</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. LO</t>
+          <t>I. BRAZDEIKIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3736</v>
+        <v>-0.1773</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0766</v>
+        <v>-0.2403</v>
       </c>
       <c r="F18" t="n">
+        <v>0.0631</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.8183</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.8618</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="K18" t="n">
         <v>-0.4502</v>
       </c>
-      <c r="G18" t="n">
-        <v>-0.5926</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-3.2291</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.6365</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.1347</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-1.4516</v>
-      </c>
       <c r="L18" t="n">
-        <v>2.5863</v>
+        <v>0.465</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7273</v>
+        <v>-0.8331</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.7775</v>
+        <v>-0.4116</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0502</v>
+        <v>-0.4216</v>
       </c>
       <c r="P18" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.227</v>
+        <v>-0.1966</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1123</v>
+        <v>-0.3969</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1147</v>
+        <v>0.2003</v>
       </c>
       <c r="V18" t="n">
-        <v>1.214</v>
+        <v>0.1418</v>
       </c>
       <c r="W18" t="n">
-        <v>1.214</v>
+        <v>0.1418</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. TUBELIS</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4811</v>
+        <v>-0.1982</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3903</v>
+        <v>0.0449</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8714</v>
+        <v>-0.2431</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3912</v>
+        <v>-0.8048</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6494</v>
+        <v>-0.9252</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0406</v>
+        <v>0.1205</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0567</v>
+        <v>0.6224</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5917</v>
+        <v>0.7597</v>
       </c>
       <c r="L19" t="n">
-        <v>0.465</v>
+        <v>-0.1373</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6655</v>
+        <v>-1.4272</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.241</v>
+        <v>-1.6849</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5756</v>
+        <v>0.2578</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.246</v>
+        <v>-0.1768</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1845</v>
+        <v>-0.5775</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0615</v>
+        <v>0.4007</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3943</v>
+        <v>-1.0722</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>-1.0722</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2628</v>
+        <v>-0.628</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4985</v>
+        <v>-1.1447</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2357</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1499</v>
@@ -2014,13 +2014,13 @@
         <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5768</v>
+        <v>0.058</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2987</v>
+        <v>0.0551</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2781</v>
+        <v>0.0029</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>A. TUBELIS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6529</v>
+        <v>-0.7284</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7806999999999999</v>
+        <v>-0.0815</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8722</v>
+        <v>-0.6469</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8048</v>
+        <v>0.3912</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9252</v>
+        <v>-0.6494</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1205</v>
+        <v>1.0406</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6224</v>
+        <v>1.0567</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7597</v>
+        <v>0.5917</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1373</v>
+        <v>0.465</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4272</v>
+        <v>-0.6655</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6849</v>
+        <v>-1.241</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2578</v>
+        <v>0.5756</v>
       </c>
       <c r="P21" t="n">
-        <v>1.8556</v>
+        <v>-0.232</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6316</v>
+        <v>-0.4933</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.4031</v>
+        <v>-0.6563</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2284</v>
+        <v>0.163</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0722</v>
+        <v>-0.3943</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X21" t="n">
         <v>-1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7485</v>
+        <v>-1.3217</v>
       </c>
       <c r="E22" t="n">
-        <v>1.6009</v>
+        <v>1.8368</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.3494</v>
+        <v>-3.1585</v>
       </c>
       <c r="G22" t="n">
         <v>0.5229</v>
@@ -2170,13 +2170,13 @@
         <v>0.4639</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5909</v>
+        <v>-0.1641</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2161</v>
+        <v>0.0198</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3747</v>
+        <v>-0.1838</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1444</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8265</v>
+        <v>-1.8557</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6473</v>
+        <v>-3.2935</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8208</v>
+        <v>1.4378</v>
       </c>
       <c r="G23" t="n">
         <v>-0.2631</v>
@@ -2248,13 +2248,13 @@
         <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3315</v>
+        <v>-0.3607</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.187</v>
+        <v>-0.8331</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1445</v>
+        <v>0.4725</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5361</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>4.856200000000001</v>
+        <v>8.001599999999998</v>
       </c>
       <c r="E24" t="n">
-        <v>5.048</v>
+        <v>5.047899999999998</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1918</v>
+        <v>2.9537</v>
       </c>
       <c r="G24" t="n">
         <v>5.319500000000001</v>
@@ -2302,7 +2302,7 @@
         <v>13.7788</v>
       </c>
       <c r="K24" t="n">
-        <v>1.918299999999999</v>
+        <v>1.9183</v>
       </c>
       <c r="L24" t="n">
         <v>11.8605</v>
@@ -2311,7 +2311,7 @@
         <v>-8.459299999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>-9.480499999999999</v>
+        <v>-9.480500000000001</v>
       </c>
       <c r="O24" t="n">
         <v>1.0212</v>
@@ -2326,19 +2326,19 @@
         <v>12.7574</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.2262</v>
+        <v>-1.0807</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.378200000000001</v>
+        <v>-3.3783</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8478</v>
+        <v>2.2978</v>
       </c>
       <c r="V24" t="n">
         <v>0.2835999999999996</v>
       </c>
       <c r="W24" t="n">
-        <v>3.925599999999999</v>
+        <v>3.9256</v>
       </c>
       <c r="X24" t="n">
         <v>-3.642</v>
